--- a/artfynd/A 63539-2025 artfynd.xlsx
+++ b/artfynd/A 63539-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102802977</v>
+        <v>105374531</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bäcken, Tärnanområdet, Upl</t>
+          <t>Bomans udde, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689838.3248865758</v>
+        <v>689833</v>
       </c>
       <c r="R2" t="n">
-        <v>6608733.061708818</v>
+        <v>6608833</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +772,109 @@
           <t>Tomas Fridström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>102802977</v>
+      </c>
+      <c r="B3" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bäcken, Tärnanområdet, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>689839</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6608734</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-08-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-08-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Nya Tärnan gruppen</t>
         </is>
